--- a/evaluation_forms/027_research_evaluation--evaluation_forms.xlsx
+++ b/evaluation_forms/027_research_evaluation--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'name':_'clear',_'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'name': 'clear', 'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'name':_'confusing',_'label':_'confusing'}</t>
+          <t>confusing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'name': 'confusing', 'label': 'Confusing'}</t>
+          <t>Confusing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'name': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4.4,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4.4, 'name': 'good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4.5,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4.5, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4.6,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4.6, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'name':_'neither_satisfied',_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'name': 'neither_satisfied', 'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5.4,_'name':_'somewhat_dissatisfied',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5.4, 'name': 'somewhat_dissatisfied', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5.5,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5.5, 'name': 'very_dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'name':_'neither_satisfied',_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'name': 'neither_satisfied', 'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_6.4,_'name':_'somewhat_dissatisfied',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 6.4, 'name': 'somewhat_dissatisfied', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_6.5,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 6.5, 'name': 'very_dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'name':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'name': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'name':_'incomplete',_'label':_'incomplete'}</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'name': 'incomplete', 'label': 'Incomplete'}</t>
+          <t>Incomplete</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'name':_'partially_completed',_'label':_'partially_completed'}</t>
+          <t>partially_completed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'name': 'partially_completed', 'label': 'Partially Completed'}</t>
+          <t>Partially Completed</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'name': 'good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_11.3,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 11.3, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_12.1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 12.1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_12.2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 12.2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_12.3,_'name':_'neither_satisfied',_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 12.3, 'name': 'neither_satisfied', 'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_12.4,_'name':_'somewhat_dissatisfied',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 12.4, 'name': 'somewhat_dissatisfied', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_12.5,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 12.5, 'name': 'very_dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_13.3,_'name':_'neither_satisfied',_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 13.3, 'name': 'neither_satisfied', 'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_13.4,_'name':_'somewhat_dissatisfied',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 13.4, 'name': 'somewhat_dissatisfied', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_13.5,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 13.5, 'name': 'very_dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_14.3,_'name':_'neither_satisfied',_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 14.3, 'name': 'neither_satisfied', 'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_14.4,_'name':_'somewhat_dissatisfied',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 14.4, 'name': 'somewhat_dissatisfied', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_14.5,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 14.5, 'name': 'very_dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_15.1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 15.1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_15.2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 15.2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_15.3,_'name':_'neither_satisfied',_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 15.3, 'name': 'neither_satisfied', 'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_15.4,_'name':_'somewhat_dissatisfied',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 15.4, 'name': 'somewhat_dissatisfied', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_15.5,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 15.5, 'name': 'very_dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'name':_'less_than_30_minutes',_'label':_'less_than_30_minutes'}</t>
+          <t>less_than_30_minutes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'name': 'less_than_30_minutes', 'label': 'Less than 30 minutes'}</t>
+          <t>Less than 30 minutes</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'name':_'more_than_30_minutes',_'label':_'more_than_30_minutes'}</t>
+          <t>more_than_30_minutes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'name': 'more_than_30_minutes', 'label': 'More than 30 minutes'}</t>
+          <t>More than 30 minutes</t>
         </is>
       </c>
     </row>
